--- a/WAIT_AND_HOPE.xlsx
+++ b/WAIT_AND_HOPE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15420" tabRatio="654"/>
+    <workbookView windowHeight="15420" tabRatio="693"/>
   </bookViews>
   <sheets>
     <sheet name="策略" sheetId="1" r:id="rId1"/>
@@ -21,13 +21,14 @@
     <sheet name="地产等权" sheetId="7" r:id="rId12"/>
     <sheet name="基建" sheetId="10" r:id="rId13"/>
     <sheet name="养老" sheetId="11" r:id="rId14"/>
+    <sheet name="中证红利" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43">
   <si>
     <t>军工</t>
   </si>
@@ -84,6 +85,9 @@
   </si>
   <si>
     <t>中小板</t>
+  </si>
+  <si>
+    <t>中证红利</t>
   </si>
   <si>
     <t>PE 11.38/34.76%</t>
@@ -148,18 +152,24 @@
   <si>
     <t>PB 2.98/47.45%</t>
   </si>
+  <si>
+    <t>PE  6.65/11.28%</t>
+  </si>
+  <si>
+    <t>PB 0.76/0.08%</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="7" formatCode="&quot;￥&quot;#,##0.00;&quot;￥&quot;\-#,##0.00"/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -180,13 +190,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF00B050"/>
       <name val="宋体"/>
@@ -198,6 +201,13 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -235,11 +245,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -250,18 +259,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -273,31 +290,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -305,15 +300,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -335,6 +322,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -348,22 +350,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,7 +400,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,13 +424,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,12 +454,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -444,7 +466,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -456,13 +484,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -474,103 +568,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,6 +627,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -626,17 +657,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,27 +684,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -686,85 +702,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -773,66 +789,66 @@
     <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -863,19 +879,13 @@
     <xf numFmtId="7" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="7" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="7" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="7" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="7" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
@@ -887,19 +897,16 @@
     <xf numFmtId="7" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="7" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="7" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
@@ -914,13 +921,13 @@
     <xf numFmtId="7" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="10" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="41" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -992,15 +999,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>215661</xdr:rowOff>
+      <xdr:colOff>19685</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>215265</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>313729</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>62865</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1203325</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>189865</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1009,14 +1016,17 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="4015105"/>
-          <a:ext cx="3556635" cy="3200400"/>
+          <a:off x="19685" y="4909185"/>
+          <a:ext cx="2072640" cy="645160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="9525" cap="flat" cmpd="sng">
           <a:solidFill>
@@ -1078,19 +1088,6 @@
             </a:rPr>
             <a:t>存量资金分批买入</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100">
-            <a:solidFill>
-              <a:srgbClr val="000000"/>
-            </a:solidFill>
-            <a:latin typeface="宋体" charset="0"/>
-            <a:ea typeface="宋体" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
@@ -1102,7 +1099,27 @@
               <a:latin typeface="宋体" charset="0"/>
               <a:ea typeface="宋体" charset="0"/>
             </a:rPr>
-            <a:t>宁愿少赚一点，也不买高</a:t>
+            <a:t>宁愿少</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="宋体" charset="0"/>
+              <a:ea typeface="宋体" charset="0"/>
+            </a:rPr>
+            <a:t>买</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="宋体" charset="0"/>
+              <a:ea typeface="宋体" charset="0"/>
+            </a:rPr>
+            <a:t>一点，也不买高</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100">
             <a:solidFill>
@@ -1380,6 +1397,7 @@
   <dimension ref="A2:J17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
     <col min="2" max="2" width="20.8303571428571" customWidth="1"/>
     <col min="3" max="3" width="15.7678571428571" customWidth="1"/>
     <col min="4" max="5" width="20.8303571428571" customWidth="1"/>
@@ -1404,26 +1422,26 @@
       </c>
       <c r="C2" s="6">
         <f>军工!D41</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="D2" s="5">
         <f>B2/B17</f>
-        <v>0.0395599725483833</v>
+        <v>0.0387182065880863</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="2">
         <v>43940</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="27" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1437,11 +1455,11 @@
       </c>
       <c r="C3" s="6">
         <f>银行!D41</f>
-        <v>0</v>
+        <v>4089.7624</v>
       </c>
       <c r="D3" s="5">
         <f>B3/B17</f>
-        <v>0.101119305170881</v>
+        <v>0.0989676659371173</v>
       </c>
       <c r="E3" s="5"/>
       <c r="G3" s="3" t="s">
@@ -1471,7 +1489,7 @@
       </c>
       <c r="D4" s="5">
         <f>B4/B17</f>
-        <v>0.0679400947960657</v>
+        <v>0.0664944502352981</v>
       </c>
       <c r="E4" s="5"/>
       <c r="G4" s="3" t="s">
@@ -1497,11 +1515,11 @@
       </c>
       <c r="C5" s="6">
         <f>证券!D41</f>
-        <v>75311.670611</v>
+        <v>3100</v>
       </c>
       <c r="D5" s="5">
         <f>B5/B17</f>
-        <v>0.0271760379184263</v>
+        <v>0.0265977800941193</v>
       </c>
       <c r="E5" s="5"/>
     </row>
@@ -1519,7 +1537,7 @@
       </c>
       <c r="D6" s="5">
         <f>B6/B17</f>
-        <v>0.0461992644613246</v>
+        <v>0.0452162261600027</v>
       </c>
       <c r="E6" s="5"/>
     </row>
@@ -1537,7 +1555,7 @@
       </c>
       <c r="D7" s="5">
         <f>B7/B17</f>
-        <v>0.065222491004223</v>
+        <v>0.0638346722258862</v>
       </c>
       <c r="E7" s="5"/>
     </row>
@@ -1555,7 +1573,7 @@
       </c>
       <c r="D8" s="5">
         <f>B8/B17</f>
-        <v>0.135880189592131</v>
+        <v>0.132988900470596</v>
       </c>
       <c r="E8" s="5"/>
     </row>
@@ -1573,7 +1591,7 @@
       </c>
       <c r="D9" s="5">
         <f>B9/B17</f>
-        <v>0.0733753023797509</v>
+        <v>0.071814006254122</v>
       </c>
       <c r="E9" s="5"/>
     </row>
@@ -1591,7 +1609,7 @@
       </c>
       <c r="D10" s="5">
         <f>B10/B17</f>
-        <v>0.0304515657687342</v>
+        <v>0.0298036105288635</v>
       </c>
       <c r="E10" s="5"/>
     </row>
@@ -1609,7 +1627,7 @@
       </c>
       <c r="D11" s="5">
         <f>B11/B17</f>
-        <v>0.0733753023797509</v>
+        <v>0.071814006254122</v>
       </c>
       <c r="E11" s="5"/>
     </row>
@@ -1627,7 +1645,7 @@
       </c>
       <c r="D12" s="5">
         <f>B12/B17</f>
-        <v>0.108704151673705</v>
+        <v>0.106391120376477</v>
       </c>
       <c r="E12" s="5"/>
     </row>
@@ -1645,7 +1663,7 @@
       </c>
       <c r="D13" s="5">
         <f>B13/B17</f>
-        <v>0.0815281137552788</v>
+        <v>0.0797933402823578</v>
       </c>
       <c r="E13" s="5"/>
     </row>
@@ -1663,16 +1681,40 @@
       </c>
       <c r="D14" s="5">
         <f>B14/B17</f>
-        <v>0.149468208551344</v>
+        <v>0.146287790517656</v>
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="12">
-        <f>SUM(B2:B14)</f>
-        <v>586451.367518659</v>
-      </c>
-      <c r="C17" s="29"/>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="6">
+        <f>中证红利!C41</f>
+        <v>12749.9396808</v>
+      </c>
+      <c r="C15" s="6">
+        <f>中证红利!D41</f>
+        <v>800</v>
+      </c>
+      <c r="D15" s="5">
+        <f>B15/B17</f>
+        <v>0.0212782240752954</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="10">
+        <f>SUM(B2:B15)</f>
+        <v>599201.307199459</v>
+      </c>
+      <c r="C17" s="23">
+        <f>SUM(C2:C15)</f>
+        <v>45710.2924</v>
+      </c>
+      <c r="D17" s="26">
+        <f>C17/B17</f>
+        <v>0.0762853682907341</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1719,9 +1761,9 @@
     </row>
     <row r="2" customFormat="1" spans="4:22">
       <c r="D2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="15"/>
+        <v>30</v>
+      </c>
+      <c r="K2" s="13"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -1731,11 +1773,11 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="V2" s="17"/>
+      <c r="V2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="4:20">
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="4"/>
@@ -1771,7 +1813,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -1834,7 +1876,7 @@
         <f t="shared" si="1"/>
         <v>132.86025</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:11">
       <c r="A8" s="4">
@@ -1963,7 +2005,7 @@
         <f>C13*1.1</f>
         <v>275</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:11">
       <c r="A15" s="4">
@@ -2158,10 +2200,10 @@
         <f>C30</f>
         <v>1000</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2178,15 +2220,15 @@
         <f t="shared" ref="C31:C39" si="2">C30*1.1</f>
         <v>1100</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="9">
         <f>SUM(C30:C31)</f>
         <v>2100</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-50.0000000000001</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -2204,15 +2246,12 @@
         <f t="shared" si="2"/>
         <v>1210</v>
       </c>
-      <c r="D32" s="21">
-        <f>SUM(C30:C32)</f>
-        <v>3310</v>
-      </c>
-      <c r="E32" s="13">
+      <c r="D32" s="19"/>
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-137.3725</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.0415022658610272</v>
       </c>
@@ -2230,15 +2269,12 @@
         <f t="shared" si="2"/>
         <v>1331</v>
       </c>
-      <c r="D33" s="21">
-        <f>SUM(C30:C33)</f>
-        <v>4641</v>
-      </c>
-      <c r="E33" s="13">
+      <c r="D33" s="19"/>
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-333.011695906433</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
         <v>-0.0717542977604898</v>
       </c>
@@ -2256,15 +2292,12 @@
         <f t="shared" si="2"/>
         <v>1464.1</v>
       </c>
-      <c r="D34" s="21">
-        <f>SUM(C30:C34)</f>
-        <v>6105.1</v>
-      </c>
-      <c r="E34" s="13">
+      <c r="D34" s="19"/>
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-586.422772617819</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0960545728354685</v>
       </c>
@@ -2282,15 +2315,12 @@
         <f t="shared" si="2"/>
         <v>1610.51</v>
       </c>
-      <c r="D35" s="21">
-        <f>SUM(C30:C35)</f>
-        <v>7715.61</v>
-      </c>
-      <c r="E35" s="13">
+      <c r="D35" s="19"/>
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-931.340099329205</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -2308,15 +2338,12 @@
         <f t="shared" si="2"/>
         <v>1771.561</v>
       </c>
-      <c r="D36" s="21">
-        <f>SUM(C30:C36)</f>
-        <v>9487.171</v>
-      </c>
-      <c r="E36" s="13">
+      <c r="D36" s="19"/>
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-1383.62475937393</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -2330,19 +2357,16 @@
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="17">
         <f t="shared" si="2"/>
         <v>1948.7171</v>
       </c>
-      <c r="D37" s="21">
-        <f>SUM(C30:C37)</f>
-        <v>11435.8881</v>
-      </c>
-      <c r="E37" s="13">
+      <c r="D37" s="19"/>
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-1962.44949084722</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -2356,19 +2380,16 @@
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="17">
         <f t="shared" si="2"/>
         <v>2143.58881</v>
       </c>
-      <c r="D38" s="21">
-        <f>SUM(C30:C38)</f>
-        <v>13579.47691</v>
-      </c>
-      <c r="E38" s="13">
+      <c r="D38" s="19"/>
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-2691.17553770512</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -2382,31 +2403,28 @@
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="17">
         <f t="shared" si="2"/>
         <v>2357.947691</v>
       </c>
-      <c r="D39" s="21">
+      <c r="D39" s="19"/>
+      <c r="E39" s="11">
+        <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
+        <v>-3598.53398539636</v>
+      </c>
+      <c r="F39" s="12">
+        <f>E39/SUM(C30:C39)</f>
+        <v>-0.225791435911833</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>15937.424601</v>
       </c>
-      <c r="E39" s="13">
-        <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
-        <v>-3598.53398539636</v>
-      </c>
-      <c r="F39" s="14">
-        <f>E39/SUM(C30:C39)</f>
-        <v>-0.225791435911833</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4">
-      <c r="C41" s="12">
-        <f>SUM(C30:C39)</f>
-        <v>15937.424601</v>
-      </c>
       <c r="D41" s="9">
         <f>SUM(D30:D39)</f>
-        <v>75311.670611</v>
+        <v>3100</v>
       </c>
     </row>
   </sheetData>
@@ -2447,9 +2465,9 @@
     </row>
     <row r="2" spans="4:22">
       <c r="D2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="15"/>
+        <v>32</v>
+      </c>
+      <c r="K2" s="13"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -2459,11 +2477,11 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="V2" s="17"/>
+      <c r="V2" s="15"/>
     </row>
     <row r="3" spans="4:20">
       <c r="D3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -2495,7 +2513,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -2557,7 +2575,7 @@
         <f t="shared" si="1"/>
         <v>132.86025</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4">
@@ -2670,7 +2688,7 @@
         <f>C13*1.1</f>
         <v>275</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4">
@@ -2847,7 +2865,7 @@
         <v>575</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2865,10 +2883,10 @@
         <f>C30</f>
         <v>1600</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2885,12 +2903,12 @@
         <f>C30*1.1</f>
         <v>1760</v>
       </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="13">
+      <c r="D31" s="19"/>
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-80</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -2908,12 +2926,12 @@
         <f>C30*1.2</f>
         <v>1920</v>
       </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="13">
+      <c r="D32" s="19"/>
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-215.0715</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.0407332386363636</v>
       </c>
@@ -2931,12 +2949,12 @@
         <f>C30*1.3</f>
         <v>2080</v>
       </c>
-      <c r="D33" s="21"/>
-      <c r="E33" s="13">
+      <c r="D33" s="19"/>
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-531.929824561404</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
         <v>-0.0722730739893211</v>
       </c>
@@ -2954,12 +2972,12 @@
         <f>C30*1.4</f>
         <v>2240</v>
       </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="13">
+      <c r="D34" s="19"/>
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-933.581011351909</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0972480220158238</v>
       </c>
@@ -2969,7 +2987,7 @@
         <f>A30*0.75</f>
         <v>826.0725</v>
       </c>
-      <c r="B35" s="22">
+      <c r="B35" s="5">
         <f>(A35-A30)/A30</f>
         <v>-0.25</v>
       </c>
@@ -2977,12 +2995,12 @@
         <f>C30*1.5</f>
         <v>2400</v>
       </c>
-      <c r="D35" s="21"/>
-      <c r="E35" s="13">
+      <c r="D35" s="19"/>
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-1475.23219814242</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.122936016511868</v>
       </c>
@@ -2992,7 +3010,7 @@
         <f>A30*0.7</f>
         <v>771.001</v>
       </c>
-      <c r="B36" s="22">
+      <c r="B36" s="5">
         <f>(A36-A30)/A30</f>
         <v>-0.3</v>
       </c>
@@ -3000,12 +3018,12 @@
         <f>C30*1.6</f>
         <v>2560</v>
       </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="13">
+      <c r="D36" s="19"/>
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-2176.88338493292</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.149511221492646</v>
       </c>
@@ -3015,7 +3033,7 @@
         <f>A30*0.65</f>
         <v>715.9295</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="16">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
@@ -3023,12 +3041,12 @@
         <f>C30*1.7</f>
         <v>2720</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="13">
+      <c r="D37" s="19"/>
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-3061.39171458057</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.177163872371561</v>
       </c>
@@ -3038,7 +3056,7 @@
         <f>A30*0.6</f>
         <v>660.858</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="16">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
@@ -3046,12 +3064,12 @@
         <f>C30*1.8</f>
         <v>2880</v>
       </c>
-      <c r="D38" s="21"/>
-      <c r="E38" s="13">
+      <c r="D38" s="19"/>
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-4155.13081345899</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.206107679239037</v>
       </c>
@@ -3061,7 +3079,7 @@
         <f>A30*0.55</f>
         <v>605.7865</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="16">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
@@ -3069,20 +3087,24 @@
         <f>C30*1.9</f>
         <v>3040</v>
       </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="13">
+      <c r="D39" s="19"/>
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-5488.8699123374</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.236589220359371</v>
       </c>
     </row>
-    <row r="41" spans="3:3">
-      <c r="C41" s="12">
+    <row r="41" spans="3:4">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>23200</v>
+      </c>
+      <c r="D41" s="9">
+        <f>SUM(D30:D39)</f>
+        <v>1600</v>
       </c>
     </row>
   </sheetData>
@@ -3123,9 +3145,9 @@
     </row>
     <row r="2" customFormat="1" spans="4:22">
       <c r="D2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="15"/>
+        <v>35</v>
+      </c>
+      <c r="K2" s="13"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -3135,11 +3157,11 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="V2" s="17"/>
+      <c r="V2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="4:20">
       <c r="D3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="4"/>
@@ -3175,7 +3197,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -3238,7 +3260,7 @@
         <f t="shared" si="1"/>
         <v>132.86025</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:11">
       <c r="A8" s="4">
@@ -3367,7 +3389,7 @@
         <f>C13*1.1</f>
         <v>275</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:11">
       <c r="A15" s="4">
@@ -3562,10 +3584,10 @@
         <f>C30</f>
         <v>2400</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3582,11 +3604,11 @@
         <f>C30*1.1</f>
         <v>2640</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-120</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -3604,11 +3626,11 @@
         <f t="shared" ref="C32:C39" si="2">C31*1.1</f>
         <v>2904</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-580.121</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.0730263091641491</v>
       </c>
@@ -3626,11 +3648,11 @@
         <f t="shared" si="2"/>
         <v>3194.4</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-799.228070175439</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
         <v>-0.0717542977604897</v>
       </c>
@@ -3648,11 +3670,11 @@
         <f t="shared" si="2"/>
         <v>3513.84</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-1407.41465428276</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0960545728354685</v>
       </c>
@@ -3670,11 +3692,11 @@
         <f t="shared" si="2"/>
         <v>3865.224</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-2235.21623839009</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -3692,11 +3714,11 @@
         <f t="shared" si="2"/>
         <v>4251.7464</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-3320.69942249742</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -3706,20 +3728,20 @@
         <f>A30*0.65</f>
         <v>4421.573</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="16">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="17">
         <f t="shared" si="2"/>
         <v>4676.92104</v>
       </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="13">
+      <c r="D37" s="18"/>
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-4709.87877803332</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -3729,20 +3751,20 @@
         <f>A30*0.6</f>
         <v>4081.452</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="16">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="17">
         <f t="shared" si="2"/>
         <v>5144.613144</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="13">
+      <c r="D38" s="18"/>
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-6458.8212904923</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -3752,26 +3774,26 @@
         <f>A30*0.55</f>
         <v>3741.331</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="16">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="17">
         <f t="shared" si="2"/>
         <v>5659.0744584</v>
       </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="13">
+      <c r="D39" s="18"/>
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-8636.48156495127</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.225791435911833</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="12">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>38249.8190424</v>
       </c>
@@ -3820,9 +3842,9 @@
     <row r="2" customFormat="1" spans="1:22">
       <c r="A2" s="3"/>
       <c r="D2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="K2" s="13"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -3832,12 +3854,12 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="V2" s="17"/>
+      <c r="V2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="1:20">
       <c r="A3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="4"/>
@@ -3873,7 +3895,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -3936,7 +3958,7 @@
         <f t="shared" si="1"/>
         <v>132.86025</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:11">
       <c r="A8" s="4">
@@ -4065,7 +4087,7 @@
         <f>C13*1.1</f>
         <v>275</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:11">
       <c r="A15" s="4">
@@ -4260,10 +4282,10 @@
         <f>C30</f>
         <v>1120.53</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4280,11 +4302,11 @@
         <f>C30*1.1</f>
         <v>1232.583</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-56.0265000000001</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -4302,13 +4324,13 @@
         <f t="shared" ref="C32:C39" si="2">C31*1.1</f>
         <v>1355.8413</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-290.8065</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
-        <v>-0.0784066010195919</v>
+        <v>-0.078406601019592</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4324,11 +4346,11 @@
         <f t="shared" si="2"/>
         <v>1491.42543</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-373.149595614035</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
         <v>-0.0717542977604897</v>
       </c>
@@ -4346,13 +4368,13 @@
         <f t="shared" si="2"/>
         <v>1640.567973</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
-        <v>-657.104309401444</v>
-      </c>
-      <c r="F34" s="14">
+        <v>-657.104309401445</v>
+      </c>
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
-        <v>-0.0960545728354684</v>
+        <v>-0.0960545728354685</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4368,11 +4390,11 @@
         <f t="shared" si="2"/>
         <v>1804.6247703</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
-        <v>-1043.59452150135</v>
-      </c>
-      <c r="F35" s="14">
+        <v>-1043.59452150136</v>
+      </c>
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -4390,11 +4412,11 @@
         <f t="shared" si="2"/>
         <v>1985.08724733</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-1550.39305162126</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -4404,19 +4426,19 @@
         <f>A30*0.65</f>
         <v>2323.7955</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="5">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="6">
         <f t="shared" si="2"/>
         <v>2183.595972063</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-2198.98352797903</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -4426,19 +4448,19 @@
         <f>A30*0.6</f>
         <v>2145.042</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="5">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="6">
         <f t="shared" si="2"/>
         <v>2401.9555692693</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-3015.54292526472</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -4448,25 +4470,25 @@
         <f>A30*0.55</f>
         <v>1966.2885</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="5">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="6">
         <f t="shared" si="2"/>
         <v>2642.15112619623</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-4032.26528665619</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.225791435911833</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="12">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>17858.3623881585</v>
       </c>
@@ -4513,9 +4535,9 @@
     </row>
     <row r="2" customFormat="1" spans="4:22">
       <c r="D2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="15"/>
+        <v>39</v>
+      </c>
+      <c r="K2" s="13"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -4525,11 +4547,11 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="V2" s="17"/>
+      <c r="V2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="4:20">
       <c r="D3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="4"/>
@@ -4565,7 +4587,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -4628,7 +4650,7 @@
         <f t="shared" si="1"/>
         <v>132.86025</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:11">
       <c r="A8" s="4">
@@ -4757,7 +4779,7 @@
         <f>C13*1.1</f>
         <v>275</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:11">
       <c r="A15" s="4">
@@ -4952,10 +4974,10 @@
         <f>C30</f>
         <v>2700</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -4972,11 +4994,11 @@
         <f>C30*1.1</f>
         <v>2970</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-135</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -4994,11 +5016,11 @@
         <f t="shared" ref="C32:C39" si="2">C31*1.1</f>
         <v>3267</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-654.2585</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.0732078437954571</v>
       </c>
@@ -5016,11 +5038,11 @@
         <f t="shared" si="2"/>
         <v>3593.7</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-899.131578947368</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
         <v>-0.0717542977604897</v>
       </c>
@@ -5038,11 +5060,11 @@
         <f t="shared" si="2"/>
         <v>3953.07</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-1583.34148606811</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0960545728354685</v>
       </c>
@@ -5060,11 +5082,11 @@
         <f t="shared" si="2"/>
         <v>4348.377</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
-        <v>-2514.61826818885</v>
-      </c>
-      <c r="F35" s="14">
+        <v>-2514.61826818886</v>
+      </c>
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -5082,11 +5104,11 @@
         <f t="shared" si="2"/>
         <v>4783.2147</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-3735.7868503096</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -5096,19 +5118,19 @@
         <f>A30*0.65</f>
         <v>4995.3605</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="5">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="6">
         <f t="shared" si="2"/>
         <v>5261.53617</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
-        <v>-5298.61362528749</v>
-      </c>
-      <c r="F37" s="14">
+        <v>-5298.61362528748</v>
+      </c>
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -5118,19 +5140,19 @@
         <f>A30*0.6</f>
         <v>4611.102</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="5">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="6">
         <f t="shared" si="2"/>
         <v>5787.689787</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
-        <v>-7266.17395180384</v>
-      </c>
-      <c r="F38" s="14">
+        <v>-7266.17395180383</v>
+      </c>
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -5140,25 +5162,25 @@
         <f>A30*0.55</f>
         <v>4226.8435</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="5">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="6">
         <f t="shared" si="2"/>
-        <v>6366.45876570001</v>
-      </c>
-      <c r="E39" s="13">
+        <v>6366.4587657</v>
+      </c>
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-9716.04176057018</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.225791435911833</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="12">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>43031.0464227</v>
       </c>
@@ -5166,6 +5188,728 @@
         <f>SUM(D30:D39)</f>
         <v>2700</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr/>
+  <dimension ref="A1:X41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <cols>
+    <col min="1" max="2" width="15.7767857142857" customWidth="1"/>
+    <col min="3" max="3" width="21.1339285714286" customWidth="1"/>
+    <col min="4" max="4" width="12.7857142857143" customWidth="1"/>
+    <col min="5" max="5" width="12.0535714285714" customWidth="1"/>
+    <col min="6" max="6" width="16.2142857142857" customWidth="1"/>
+    <col min="7" max="8" width="12.7857142857143" customWidth="1"/>
+    <col min="9" max="9" width="13.6964285714286" customWidth="1"/>
+    <col min="10" max="10" width="10.7857142857143" customWidth="1"/>
+    <col min="11" max="11" width="15.9196428571429" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.0892857142857" customWidth="1"/>
+    <col min="13" max="21" width="10.7857142857143" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
+    <col min="23" max="23" width="10.7857142857143" customWidth="1"/>
+    <col min="24" max="24" width="12.6517857142857" customWidth="1"/>
+    <col min="25" max="25" width="17.5625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="1" spans="2:11">
+      <c r="B1" s="2"/>
+      <c r="D1" s="2">
+        <v>43952</v>
+      </c>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" customFormat="1" spans="4:22">
+      <c r="D2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="V2" s="15"/>
+    </row>
+    <row r="3" customFormat="1" spans="4:20">
+      <c r="D3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+    </row>
+    <row r="4" customFormat="1" spans="11:11">
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" customFormat="1" spans="1:24">
+      <c r="A5" s="4">
+        <f t="shared" ref="A5:A12" si="0">A6*105%</f>
+        <v>7253.00606821376</v>
+      </c>
+      <c r="B5" s="5">
+        <f>(A5-A13)/A13</f>
+        <v>0.477455443789063</v>
+      </c>
+      <c r="C5" s="6">
+        <f t="shared" ref="C5:C12" si="1">C6*0.9</f>
+        <v>107.6168025</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+    </row>
+    <row r="6" customFormat="1" spans="1:24">
+      <c r="A6" s="4">
+        <f t="shared" si="0"/>
+        <v>6907.62482687025</v>
+      </c>
+      <c r="B6" s="5">
+        <f>(A6-A13)/A13</f>
+        <v>0.40710042265625</v>
+      </c>
+      <c r="C6" s="6">
+        <f t="shared" si="1"/>
+        <v>119.574225</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+    </row>
+    <row r="7" customFormat="1" spans="1:11">
+      <c r="A7" s="4">
+        <f t="shared" si="0"/>
+        <v>6578.690311305</v>
+      </c>
+      <c r="B7" s="5">
+        <f>(A7-A13)/A13</f>
+        <v>0.340095640625</v>
+      </c>
+      <c r="C7" s="6">
+        <f t="shared" si="1"/>
+        <v>132.86025</v>
+      </c>
+      <c r="K7" s="14"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:11">
+      <c r="A8" s="4">
+        <f t="shared" si="0"/>
+        <v>6265.4193441</v>
+      </c>
+      <c r="B8" s="5">
+        <f>(A8-A13)/A13</f>
+        <v>0.2762815625</v>
+      </c>
+      <c r="C8" s="6">
+        <f t="shared" si="1"/>
+        <v>147.6225</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:11">
+      <c r="A9" s="4">
+        <f t="shared" si="0"/>
+        <v>5967.066042</v>
+      </c>
+      <c r="B9" s="5">
+        <f>(A9-A13)/A13</f>
+        <v>0.21550625</v>
+      </c>
+      <c r="C9" s="6">
+        <f t="shared" si="1"/>
+        <v>164.025</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:11">
+      <c r="A10" s="4">
+        <f t="shared" si="0"/>
+        <v>5682.92004</v>
+      </c>
+      <c r="B10" s="5">
+        <f>(A10-A13)/A13</f>
+        <v>0.157625</v>
+      </c>
+      <c r="C10" s="6">
+        <f t="shared" si="1"/>
+        <v>182.25</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" customFormat="1" spans="1:11">
+      <c r="A11" s="4">
+        <f t="shared" si="0"/>
+        <v>5412.3048</v>
+      </c>
+      <c r="B11" s="5">
+        <f>(A11-A13)/A13</f>
+        <v>0.1025</v>
+      </c>
+      <c r="C11" s="6">
+        <f t="shared" si="1"/>
+        <v>202.5</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:24">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>5154.576</v>
+      </c>
+      <c r="B12" s="5">
+        <f>(A12-A13)/A13</f>
+        <v>0.05</v>
+      </c>
+      <c r="C12" s="6">
+        <f t="shared" si="1"/>
+        <v>225</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="1"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:24">
+      <c r="A13" s="7">
+        <v>4909.12</v>
+      </c>
+      <c r="B13">
+        <f>(A13-A13)/A13</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="8">
+        <v>250</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="1"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:11">
+      <c r="A14" s="4">
+        <f>A13*0.95</f>
+        <v>4663.664</v>
+      </c>
+      <c r="B14" s="5">
+        <f>(A14-A13)/A13</f>
+        <v>-0.05</v>
+      </c>
+      <c r="C14" s="6">
+        <f>C13*1.1</f>
+        <v>275</v>
+      </c>
+      <c r="K14" s="14"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:11">
+      <c r="A15" s="4">
+        <f>A13*0.9</f>
+        <v>4418.208</v>
+      </c>
+      <c r="B15" s="5">
+        <f>(A15-A13)/A13</f>
+        <v>-0.1</v>
+      </c>
+      <c r="C15" s="6">
+        <f>C13*1.2</f>
+        <v>300</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:11">
+      <c r="A16" s="4">
+        <f>A13*0.85</f>
+        <v>4172.752</v>
+      </c>
+      <c r="B16" s="5">
+        <f>(A16-A13)/A13</f>
+        <v>-0.15</v>
+      </c>
+      <c r="C16" s="6">
+        <f>C13*1.3</f>
+        <v>325</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" customFormat="1" spans="1:11">
+      <c r="A17" s="4">
+        <f>A13*0.8</f>
+        <v>3927.296</v>
+      </c>
+      <c r="B17" s="5">
+        <f>(A17-A13)/A13</f>
+        <v>-0.2</v>
+      </c>
+      <c r="C17" s="6">
+        <f>C13*1.4</f>
+        <v>350</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" customFormat="1" spans="1:11">
+      <c r="A18" s="4">
+        <f>A13*0.75</f>
+        <v>3681.84</v>
+      </c>
+      <c r="B18" s="5">
+        <f>(A18-A13)/A13</f>
+        <v>-0.25</v>
+      </c>
+      <c r="C18" s="6">
+        <f>C13*1.5</f>
+        <v>375</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" customFormat="1" spans="1:11">
+      <c r="A19" s="4">
+        <f>A13*0.7</f>
+        <v>3436.384</v>
+      </c>
+      <c r="B19" s="5">
+        <f>(A19-A13)/A13</f>
+        <v>-0.3</v>
+      </c>
+      <c r="C19" s="6">
+        <f>C13*1.6</f>
+        <v>400</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" customFormat="1" spans="1:11">
+      <c r="A20" s="4">
+        <f>A13*0.65</f>
+        <v>3190.928</v>
+      </c>
+      <c r="B20" s="5">
+        <f>(A20-A13)/A13</f>
+        <v>-0.35</v>
+      </c>
+      <c r="C20" s="6">
+        <f>C13*1.7</f>
+        <v>425</v>
+      </c>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:11">
+      <c r="A21" s="4">
+        <f>A13*0.6</f>
+        <v>2945.472</v>
+      </c>
+      <c r="B21" s="5">
+        <f>(A21-A13)/A13</f>
+        <v>-0.4</v>
+      </c>
+      <c r="C21" s="6">
+        <f>C13*1.8</f>
+        <v>450</v>
+      </c>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" customFormat="1" spans="1:11">
+      <c r="A22" s="4">
+        <f>A13*0.55</f>
+        <v>2700.016</v>
+      </c>
+      <c r="B22" s="5">
+        <f>(A22-A13)/A13</f>
+        <v>-0.45</v>
+      </c>
+      <c r="C22" s="6">
+        <f>C13*1.9</f>
+        <v>475</v>
+      </c>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" customFormat="1" spans="1:11">
+      <c r="A23" s="4">
+        <f>A13*0.5</f>
+        <v>2454.56</v>
+      </c>
+      <c r="B23" s="5">
+        <f>(A23-A13)/A13</f>
+        <v>-0.5</v>
+      </c>
+      <c r="C23" s="6">
+        <f>C13*2</f>
+        <v>500</v>
+      </c>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" customFormat="1" spans="1:11">
+      <c r="A24" s="4">
+        <f>A13*0.45</f>
+        <v>2209.104</v>
+      </c>
+      <c r="B24" s="5">
+        <f>(A24-A13)/A13</f>
+        <v>-0.55</v>
+      </c>
+      <c r="C24" s="6">
+        <f>C13*2.1</f>
+        <v>525</v>
+      </c>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" customFormat="1" spans="1:11">
+      <c r="A25" s="4">
+        <f>A13*0.4</f>
+        <v>1963.648</v>
+      </c>
+      <c r="B25" s="5">
+        <f>(A25-A13)/A13</f>
+        <v>-0.6</v>
+      </c>
+      <c r="C25" s="6">
+        <f>C13*2.2</f>
+        <v>550</v>
+      </c>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" customFormat="1" spans="1:11">
+      <c r="A26" s="4">
+        <f>A13*0.35</f>
+        <v>1718.192</v>
+      </c>
+      <c r="B26" s="5">
+        <f>(A26-A13)/A13</f>
+        <v>-0.65</v>
+      </c>
+      <c r="C26" s="6">
+        <f>C13*2.3</f>
+        <v>575</v>
+      </c>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" customFormat="1" spans="11:11">
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" customFormat="1" spans="11:11">
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" customFormat="1" spans="11:11">
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" customFormat="1" spans="1:11">
+      <c r="A30" s="7">
+        <v>4090.12</v>
+      </c>
+      <c r="B30">
+        <f>(A30-A30)/A30</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="8">
+        <v>800</v>
+      </c>
+      <c r="D30" s="9">
+        <f>C30</f>
+        <v>800</v>
+      </c>
+      <c r="E30" s="11">
+        <v>0</v>
+      </c>
+      <c r="F30" s="12">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" customFormat="1" spans="1:11">
+      <c r="A31" s="4">
+        <f>A30*0.95</f>
+        <v>3885.614</v>
+      </c>
+      <c r="B31" s="5">
+        <f>(A31-A30)/A30</f>
+        <v>-0.0500000000000001</v>
+      </c>
+      <c r="C31" s="6">
+        <f t="shared" ref="C31:C39" si="2">C30*1.1</f>
+        <v>880</v>
+      </c>
+      <c r="E31" s="11">
+        <f>(A31-A30)/A30*C30</f>
+        <v>-40.0000000000001</v>
+      </c>
+      <c r="F31" s="12">
+        <f>E31/SUM(C30:C31)</f>
+        <v>-0.0238095238095239</v>
+      </c>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" customFormat="1" spans="1:11">
+      <c r="A32" s="4">
+        <f>A30*0.9</f>
+        <v>3681.108</v>
+      </c>
+      <c r="B32" s="5">
+        <f>(A32-A30)/A30</f>
+        <v>-0.0999999999999999</v>
+      </c>
+      <c r="C32" s="6">
+        <f t="shared" si="2"/>
+        <v>968</v>
+      </c>
+      <c r="E32" s="11">
+        <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
+        <v>-284.505999999999</v>
+      </c>
+      <c r="F32" s="12">
+        <f>E32/SUM(C30:C32)</f>
+        <v>-0.107441842900302</v>
+      </c>
+      <c r="K32" s="1"/>
+    </row>
+    <row r="33" customFormat="1" spans="1:11">
+      <c r="A33" s="4">
+        <f>A30*0.85</f>
+        <v>3476.602</v>
+      </c>
+      <c r="B33" s="5">
+        <f>(A33-A30)/A30</f>
+        <v>-0.15</v>
+      </c>
+      <c r="C33" s="6">
+        <f t="shared" si="2"/>
+        <v>1064.8</v>
+      </c>
+      <c r="E33" s="11">
+        <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
+        <v>-266.409356725146</v>
+      </c>
+      <c r="F33" s="12">
+        <f>E33/SUM(C30:C33)</f>
+        <v>-0.0717542977604898</v>
+      </c>
+      <c r="K33" s="1"/>
+    </row>
+    <row r="34" customFormat="1" spans="1:11">
+      <c r="A34" s="4">
+        <f>A30*0.8</f>
+        <v>3272.096</v>
+      </c>
+      <c r="B34" s="5">
+        <f>(A34-A30)/A30</f>
+        <v>-0.2</v>
+      </c>
+      <c r="C34" s="6">
+        <f t="shared" si="2"/>
+        <v>1171.28</v>
+      </c>
+      <c r="E34" s="11">
+        <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
+        <v>-469.138218094255</v>
+      </c>
+      <c r="F34" s="12">
+        <f>E34/SUM(C30:C34)</f>
+        <v>-0.0960545728354685</v>
+      </c>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="35" customFormat="1" spans="1:11">
+      <c r="A35" s="4">
+        <f>A30*0.75</f>
+        <v>3067.59</v>
+      </c>
+      <c r="B35" s="5">
+        <f>(A35-A30)/A30</f>
+        <v>-0.25</v>
+      </c>
+      <c r="C35" s="6">
+        <f t="shared" si="2"/>
+        <v>1288.408</v>
+      </c>
+      <c r="E35" s="11">
+        <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
+        <v>-745.072079463364</v>
+      </c>
+      <c r="F35" s="12">
+        <f>E35/SUM(C30:C35)</f>
+        <v>-0.120708550500765</v>
+      </c>
+      <c r="K35" s="1"/>
+    </row>
+    <row r="36" customFormat="1" spans="1:11">
+      <c r="A36" s="4">
+        <f>A30*0.7</f>
+        <v>2863.084</v>
+      </c>
+      <c r="B36" s="5">
+        <f>(A36-A30)/A30</f>
+        <v>-0.3</v>
+      </c>
+      <c r="C36" s="6">
+        <f t="shared" si="2"/>
+        <v>1417.2488</v>
+      </c>
+      <c r="E36" s="11">
+        <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
+        <v>-1106.89980749914</v>
+      </c>
+      <c r="F36" s="12">
+        <f>E36/SUM(C30:C36)</f>
+        <v>-0.145841659159925</v>
+      </c>
+      <c r="K36" s="1"/>
+    </row>
+    <row r="37" customFormat="1" spans="1:11">
+      <c r="A37" s="4">
+        <f>A30*0.65</f>
+        <v>2658.578</v>
+      </c>
+      <c r="B37" s="5">
+        <f>(A37-A30)/A30</f>
+        <v>-0.35</v>
+      </c>
+      <c r="C37" s="6">
+        <f t="shared" si="2"/>
+        <v>1558.97368</v>
+      </c>
+      <c r="E37" s="11">
+        <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
+        <v>-1569.95959267777</v>
+      </c>
+      <c r="F37" s="12">
+        <f>E37/SUM(C30:C37)</f>
+        <v>-0.171604467767328</v>
+      </c>
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" customFormat="1" spans="1:11">
+      <c r="A38" s="4">
+        <f>A30*0.6</f>
+        <v>2454.072</v>
+      </c>
+      <c r="B38" s="5">
+        <f>(A38-A30)/A30</f>
+        <v>-0.4</v>
+      </c>
+      <c r="C38" s="6">
+        <f t="shared" si="2"/>
+        <v>1714.871048</v>
+      </c>
+      <c r="E38" s="11">
+        <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
+        <v>-2152.9404301641</v>
+      </c>
+      <c r="F38" s="12">
+        <f>E38/SUM(C30:C38)</f>
+        <v>-0.198179617340291</v>
+      </c>
+      <c r="K38" s="1"/>
+    </row>
+    <row r="39" customFormat="1" spans="1:11">
+      <c r="A39" s="4">
+        <f>A30*0.55</f>
+        <v>2249.566</v>
+      </c>
+      <c r="B39" s="5">
+        <f>(A39-A30)/A30</f>
+        <v>-0.45</v>
+      </c>
+      <c r="C39" s="6">
+        <f t="shared" si="2"/>
+        <v>1886.3581528</v>
+      </c>
+      <c r="E39" s="11">
+        <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
+        <v>-2878.82718831709</v>
+      </c>
+      <c r="F39" s="12">
+        <f>E39/SUM(C30:C39)</f>
+        <v>-0.225791435911833</v>
+      </c>
+      <c r="K39" s="1"/>
+    </row>
+    <row r="40" customFormat="1" spans="11:11">
+      <c r="K40" s="1"/>
+    </row>
+    <row r="41" customFormat="1" spans="3:11">
+      <c r="C41" s="10">
+        <f>SUM(C30:C39)</f>
+        <v>12749.9396808</v>
+      </c>
+      <c r="D41" s="9">
+        <f>SUM(D30:D39)</f>
+        <v>800</v>
+      </c>
+      <c r="K41" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
@@ -5215,7 +5959,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
-      <c r="U2" s="17"/>
+      <c r="U2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="1:19">
       <c r="A3" s="3" t="s">
@@ -5417,9 +6161,7 @@
       <c r="D13" s="7">
         <v>4252.2</v>
       </c>
-      <c r="E13" s="25">
-        <v>400</v>
-      </c>
+      <c r="E13" s="22"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -5616,10 +6358,10 @@
         <f>C13*2.3</f>
         <v>920</v>
       </c>
-      <c r="F26" s="27"/>
+      <c r="F26" s="24"/>
     </row>
     <row r="27" spans="6:6">
-      <c r="F27" s="28"/>
+      <c r="F27" s="25"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="7">
@@ -5636,10 +6378,10 @@
         <f>C30</f>
         <v>5000</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -5656,15 +6398,15 @@
         <f>C30*1.1</f>
         <v>5500</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="23">
         <f>D30*1.1</f>
         <v>5500</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-250</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -5682,11 +6424,11 @@
         <f t="shared" ref="C32:C39" si="2">C31*1.1</f>
         <v>6050</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-733.6825</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.0443312688821752</v>
       </c>
@@ -5704,13 +6446,13 @@
         <f t="shared" si="2"/>
         <v>6655</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-1665.05847953216</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
-        <v>-0.0717542977604898</v>
+        <v>-0.0717542977604897</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -5726,11 +6468,11 @@
         <f t="shared" si="2"/>
         <v>7320.5</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-2932.11386308909</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0960545728354685</v>
       </c>
@@ -5748,11 +6490,11 @@
         <f t="shared" si="2"/>
         <v>8052.55</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-4656.70049664603</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -5770,11 +6512,11 @@
         <f t="shared" si="2"/>
         <v>8857.80500000001</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-6918.12379686963</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -5784,19 +6526,19 @@
         <f>A30*0.65</f>
         <v>3037.8725</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="16">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="17">
         <f t="shared" si="2"/>
         <v>9743.58550000001</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-9812.24745423608</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -5806,19 +6548,19 @@
         <f>A30*0.6</f>
         <v>2804.19</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="16">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="17">
         <f t="shared" si="2"/>
         <v>10717.94405</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-13455.8776885256</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -5828,25 +6570,25 @@
         <f>A30*0.55</f>
         <v>2570.5075</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="16">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="17">
         <f t="shared" si="2"/>
         <v>11789.738455</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-17992.6699269818</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.225791435911833</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="12">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>79687.123005</v>
       </c>
@@ -5884,18 +6626,18 @@
     <col min="25" max="25" width="17.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="2:11">
+    <row r="1" customFormat="1" spans="1:11">
+      <c r="A1" s="2">
+        <v>43940</v>
+      </c>
       <c r="B1" s="2"/>
-      <c r="D1" s="2">
-        <v>43940</v>
-      </c>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" customFormat="1" spans="4:20">
-      <c r="D2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="15"/>
+    <row r="2" customFormat="1" spans="1:20">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="13"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -5906,9 +6648,9 @@
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
     </row>
-    <row r="3" customFormat="1" spans="4:20">
-      <c r="D3" s="3" t="s">
-        <v>20</v>
+    <row r="3" customFormat="1" spans="1:20">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="4"/>
@@ -5944,7 +6686,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -6007,7 +6749,7 @@
         <f t="shared" si="1"/>
         <v>132.86025</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:11">
       <c r="A8" s="4">
@@ -6136,7 +6878,7 @@
         <f>C13*1.1</f>
         <v>275</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:11">
       <c r="A15" s="4">
@@ -6331,10 +7073,10 @@
         <f>C30</f>
         <v>2500</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -6351,11 +7093,11 @@
         <f>C30*1.1</f>
         <v>2750</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-125</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -6373,11 +7115,11 @@
         <f t="shared" ref="C32:C39" si="2">C31*1.1</f>
         <v>3025</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-437.174499999999</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.052830755287009</v>
       </c>
@@ -6395,11 +7137,11 @@
         <f t="shared" si="2"/>
         <v>3327.5</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-832.529239766083</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
         <v>-0.0717542977604898</v>
       </c>
@@ -6417,11 +7159,11 @@
         <f t="shared" si="2"/>
         <v>3660.25</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-1466.05693154455</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0960545728354685</v>
       </c>
@@ -6439,11 +7181,11 @@
         <f t="shared" si="2"/>
         <v>4026.275</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-2328.35024832301</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -6461,11 +7203,11 @@
         <f t="shared" si="2"/>
         <v>4428.9025</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-3459.06189843481</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -6475,19 +7217,19 @@
         <f>A30*0.65</f>
         <v>2433.2685</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="16">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="17">
         <f t="shared" si="2"/>
         <v>4871.79275</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-4906.12372711804</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -6497,19 +7239,19 @@
         <f>A30*0.6</f>
         <v>2246.094</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="16">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="17">
         <f t="shared" si="2"/>
         <v>5358.972025</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-6727.93884426281</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -6519,25 +7261,25 @@
         <f>A30*0.55</f>
         <v>2058.9195</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="16">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="17">
         <f t="shared" si="2"/>
         <v>5894.8692275</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-8996.33496349091</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.225791435911833</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="12">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>39843.5615025</v>
       </c>
@@ -6586,7 +7328,7 @@
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="15"/>
+      <c r="K2" s="13"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -6596,7 +7338,7 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="V2" s="17"/>
+      <c r="V2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="1:20">
       <c r="A3" s="3" t="s">
@@ -6639,7 +7381,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -6702,7 +7444,7 @@
         <f t="shared" si="1"/>
         <v>212.5764</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:11">
       <c r="A8" s="4">
@@ -6808,9 +7550,7 @@
       <c r="D13" s="7">
         <v>3884.55</v>
       </c>
-      <c r="E13" s="25">
-        <v>400</v>
-      </c>
+      <c r="E13" s="22"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -6835,7 +7575,7 @@
         <f>C13*1.1</f>
         <v>440</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:11">
       <c r="A15" s="4">
@@ -7030,10 +7770,10 @@
         <f>C30</f>
         <v>1700</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -7050,11 +7790,11 @@
         <f>C30*1.1</f>
         <v>1870</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-85</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -7072,11 +7812,11 @@
         <f t="shared" ref="C32:C39" si="2">C31*1.1</f>
         <v>2057</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-363.6835</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.0646318642260529</v>
       </c>
@@ -7094,11 +7834,11 @@
         <f t="shared" si="2"/>
         <v>2262.7</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-566.119883040936</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
         <v>-0.0717542977604898</v>
       </c>
@@ -7116,11 +7856,11 @@
         <f t="shared" si="2"/>
         <v>2488.97</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-996.918713450292</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0960545728354685</v>
       </c>
@@ -7138,11 +7878,11 @@
         <f t="shared" si="2"/>
         <v>2737.867</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-1583.27816885965</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -7160,11 +7900,11 @@
         <f t="shared" si="2"/>
         <v>3011.6537</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-2352.16209093567</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -7174,19 +7914,19 @@
         <f>A30*0.65</f>
         <v>2517.8855</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="16">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="17">
         <f t="shared" si="2"/>
         <v>3312.81907</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-3336.16413444027</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -7196,19 +7936,19 @@
         <f>A30*0.6</f>
         <v>2324.202</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="16">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="17">
         <f t="shared" si="2"/>
         <v>3644.100977</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-4574.99841409871</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -7218,25 +7958,25 @@
         <f>A30*0.55</f>
         <v>2130.5185</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="16">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="17">
         <f t="shared" si="2"/>
         <v>4008.5110747</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-6117.50777517382</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.225791435911833</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="12">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>27093.6218217</v>
       </c>
@@ -7285,7 +8025,7 @@
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="15"/>
+      <c r="K2" s="13"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -7295,7 +8035,7 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="V2" s="17"/>
+      <c r="V2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="1:20">
       <c r="A3" s="3" t="s">
@@ -7338,7 +8078,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -7401,7 +8141,7 @@
         <f t="shared" si="1"/>
         <v>212.5764</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:11">
       <c r="A8" s="4">
@@ -7507,9 +8247,7 @@
       <c r="D13" s="7">
         <v>5196.03</v>
       </c>
-      <c r="E13" s="25">
-        <v>400</v>
-      </c>
+      <c r="E13" s="22"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -7534,7 +8272,7 @@
         <f>C13*1.1</f>
         <v>440</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:11">
       <c r="A15" s="4">
@@ -7729,10 +8467,10 @@
         <f>C30</f>
         <v>2700</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -7749,11 +8487,11 @@
         <f>C30*1.1</f>
         <v>2970</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-135</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -7771,11 +8509,11 @@
         <f t="shared" ref="C32:C39" si="2">C31*1.1</f>
         <v>3267</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-533.223999999999</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.0596647644623474</v>
       </c>
@@ -7793,13 +8531,13 @@
         <f t="shared" si="2"/>
         <v>3593.7</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
-        <v>-899.13157894737</v>
-      </c>
-      <c r="F33" s="14">
+        <v>-899.131578947369</v>
+      </c>
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
-        <v>-0.0717542977604898</v>
+        <v>-0.0717542977604897</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -7815,13 +8553,13 @@
         <f t="shared" si="2"/>
         <v>3953.07</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-1583.34148606811</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
-        <v>-0.0960545728354685</v>
+        <v>-0.0960545728354686</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -7829,19 +8567,19 @@
         <f>A30*0.75</f>
         <v>3948.36</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="5">
         <f>(A35-A30)/A30</f>
         <v>-0.25</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="6">
         <f t="shared" si="2"/>
         <v>4348.377</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-2514.61826818885</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -7851,19 +8589,19 @@
         <f>A30*0.7</f>
         <v>3685.136</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="5">
         <f>(A36-A30)/A30</f>
         <v>-0.3</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="6">
         <f t="shared" si="2"/>
         <v>4783.2147</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-3735.7868503096</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -7873,19 +8611,19 @@
         <f>A30*0.65</f>
         <v>3421.912</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="5">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="6">
         <f t="shared" si="2"/>
         <v>5261.53617</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
-        <v>-5298.61362528748</v>
-      </c>
-      <c r="F37" s="14">
+        <v>-5298.61362528749</v>
+      </c>
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -7895,19 +8633,19 @@
         <f>A30*0.6</f>
         <v>3158.688</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="5">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="6">
         <f t="shared" si="2"/>
         <v>5787.689787</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-7266.17395180383</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -7917,25 +8655,25 @@
         <f>A30*0.55</f>
         <v>2895.464</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="5">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="6">
         <f t="shared" si="2"/>
-        <v>6366.45876570001</v>
-      </c>
-      <c r="E39" s="13">
+        <v>6366.4587657</v>
+      </c>
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-9716.04176057018</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.225791435911833</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="12">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>43031.0464227</v>
       </c>
@@ -7982,9 +8720,9 @@
     </row>
     <row r="2" customFormat="1" spans="4:22">
       <c r="D2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="15"/>
+        <v>22</v>
+      </c>
+      <c r="K2" s="13"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -7994,11 +8732,11 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="V2" s="17"/>
+      <c r="V2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="4:20">
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="4"/>
@@ -8034,7 +8772,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -8097,7 +8835,7 @@
         <f t="shared" si="1"/>
         <v>132.86025</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:11">
       <c r="A8" s="4">
@@ -8226,7 +8964,7 @@
         <f>C13*1.1</f>
         <v>275</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:11">
       <c r="A15" s="4">
@@ -8421,10 +9159,10 @@
         <f>C30</f>
         <v>4000</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -8441,11 +9179,11 @@
         <f>C30*1.1</f>
         <v>4400</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-200</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -8463,11 +9201,11 @@
         <f t="shared" ref="C32:C39" si="2">C31*1.1</f>
         <v>4840</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-540.453999999999</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.0408197885196374</v>
       </c>
@@ -8485,13 +9223,13 @@
         <f t="shared" si="2"/>
         <v>5324</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-1332.04678362573</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
-        <v>-0.0717542977604897</v>
+        <v>-0.0717542977604898</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -8507,11 +9245,11 @@
         <f t="shared" si="2"/>
         <v>5856.4</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-2345.69109047127</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0960545728354685</v>
       </c>
@@ -8529,11 +9267,11 @@
         <f t="shared" si="2"/>
         <v>6442.04</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-3725.36039731682</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -8543,19 +9281,19 @@
         <f>A30*0.7</f>
         <v>1966.356</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="5">
         <f>(A36-A30)/A30</f>
         <v>-0.3</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="6">
         <f t="shared" si="2"/>
         <v>7086.244</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-5534.4990374957</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -8565,19 +9303,19 @@
         <f>A30*0.65</f>
         <v>1825.902</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="5">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="6">
         <f t="shared" si="2"/>
         <v>7794.8684</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-7849.79796338886</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -8587,19 +9325,19 @@
         <f>A30*0.6</f>
         <v>1685.448</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="5">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="6">
         <f t="shared" si="2"/>
         <v>8574.35524</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-10764.7021508205</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -8609,25 +9347,25 @@
         <f>A30*0.55</f>
         <v>1544.994</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="5">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="6">
         <f t="shared" si="2"/>
         <v>9431.790764</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
-        <v>-14394.1359415854</v>
-      </c>
-      <c r="F39" s="14">
+        <v>-14394.1359415855</v>
+      </c>
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.225791435911833</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="12">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>63749.698404</v>
       </c>
@@ -8673,9 +9411,9 @@
     </row>
     <row r="2" customFormat="1" spans="1:22">
       <c r="A2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="15"/>
+        <v>24</v>
+      </c>
+      <c r="K2" s="13"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -8685,11 +9423,11 @@
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
-      <c r="V2" s="17"/>
+      <c r="V2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="1:20">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="4"/>
@@ -8727,7 +9465,7 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -8789,7 +9527,7 @@
         <f t="shared" si="1"/>
         <v>212.5764</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:11">
       <c r="A8" s="4">
@@ -8894,9 +9632,7 @@
       <c r="D13" s="7">
         <v>5242.88</v>
       </c>
-      <c r="E13" s="25">
-        <v>400</v>
-      </c>
+      <c r="E13" s="22"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -8920,7 +9656,7 @@
         <f>C13*1.1</f>
         <v>440</v>
       </c>
-      <c r="K14" s="16"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:11">
       <c r="A15" s="4">
@@ -9115,10 +9851,10 @@
         <f>C30</f>
         <v>3000</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -9135,11 +9871,11 @@
         <f>C30*1.1</f>
         <v>3300</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-150</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -9157,13 +9893,13 @@
         <f t="shared" ref="C32:C39" si="2">C31*1.1</f>
         <v>3630</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-567.389</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
-        <v>-0.0571388721047332</v>
+        <v>-0.0571388721047331</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -9179,11 +9915,11 @@
         <f t="shared" si="2"/>
         <v>3993</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
-        <v>-999.035087719299</v>
-      </c>
-      <c r="F33" s="14">
+        <v>-999.035087719298</v>
+      </c>
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
         <v>-0.0717542977604897</v>
       </c>
@@ -9201,11 +9937,11 @@
         <f t="shared" si="2"/>
         <v>4392.3</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-1759.26831785346</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0960545728354685</v>
       </c>
@@ -9223,11 +9959,11 @@
         <f t="shared" si="2"/>
         <v>4831.53</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-2794.02029798762</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -9245,11 +9981,11 @@
         <f t="shared" si="2"/>
         <v>5314.683</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-4150.87427812178</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -9259,19 +9995,19 @@
         <f>A30*0.65</f>
         <v>3476.057</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="5">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="6">
         <f t="shared" si="2"/>
         <v>5846.1513</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-5887.34847254165</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -9281,19 +10017,19 @@
         <f>A30*0.6</f>
         <v>3208.668</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="5">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="6">
         <f t="shared" si="2"/>
         <v>6430.76643</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-8073.52661311537</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -9303,25 +10039,25 @@
         <f>A30*0.55</f>
         <v>2941.279</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="5">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="6">
         <f t="shared" si="2"/>
-        <v>7073.84307300001</v>
-      </c>
-      <c r="E39" s="13">
+        <v>7073.843073</v>
+      </c>
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-10795.6019561891</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.225791435911833</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="12">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>47812.273803</v>
       </c>
@@ -9368,9 +10104,9 @@
     </row>
     <row r="2" customFormat="1" spans="4:21">
       <c r="D2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="15"/>
+        <v>26</v>
+      </c>
+      <c r="J2" s="13"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
@@ -9380,11 +10116,11 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
-      <c r="U2" s="17"/>
+      <c r="U2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="4:19">
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="4"/>
@@ -9419,7 +10155,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
-      <c r="J5" s="15"/>
+      <c r="J5" s="13"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -9481,7 +10217,7 @@
         <f t="shared" si="1"/>
         <v>132.86025</v>
       </c>
-      <c r="J7" s="16"/>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:10">
       <c r="A8" s="4">
@@ -9608,7 +10344,7 @@
         <f>C13*1.1</f>
         <v>275</v>
       </c>
-      <c r="J14" s="16"/>
+      <c r="J14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:10">
       <c r="A15" s="4">
@@ -9803,10 +10539,10 @@
         <f>C30</f>
         <v>5500</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -9823,11 +10559,11 @@
         <f>C30*1.1</f>
         <v>6050</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-275</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095238</v>
       </c>
@@ -9845,11 +10581,11 @@
         <f t="shared" ref="C32:C39" si="2">C31*1.1</f>
         <v>6655</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-865.833</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.0475601757758857</v>
       </c>
@@ -9867,11 +10603,11 @@
         <f t="shared" si="2"/>
         <v>7320.5</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-1831.56432748538</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
         <v>-0.0717542977604897</v>
       </c>
@@ -9889,11 +10625,11 @@
         <f t="shared" si="2"/>
         <v>8052.55</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-3225.325249398</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0960545728354685</v>
       </c>
@@ -9911,11 +10647,11 @@
         <f t="shared" si="2"/>
         <v>8857.80500000001</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-5122.37054631063</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.120708550500765</v>
       </c>
@@ -9933,11 +10669,11 @@
         <f t="shared" si="2"/>
         <v>9743.58550000001</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-7609.93617655659</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.145841659159925</v>
       </c>
@@ -9947,19 +10683,19 @@
         <f>A30*0.65</f>
         <v>4105.829</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="16">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="17">
         <f t="shared" si="2"/>
         <v>10717.94405</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-10793.4721996597</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.171604467767328</v>
       </c>
@@ -9969,19 +10705,19 @@
         <f>A30*0.6</f>
         <v>3789.996</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="16">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="17">
         <f t="shared" si="2"/>
         <v>11789.738455</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-14801.4654573782</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.198179617340291</v>
       </c>
@@ -9991,25 +10727,25 @@
         <f>A30*0.55</f>
         <v>3474.163</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="16">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
-      <c r="C39" s="19">
+      <c r="C39" s="17">
         <f t="shared" si="2"/>
         <v>12968.7123005</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-19791.93691968</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.225791435911833</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="12">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>87655.8353055001</v>
       </c>
@@ -10056,9 +10792,9 @@
     </row>
     <row r="2" customFormat="1" spans="4:21">
       <c r="D2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="15"/>
+        <v>28</v>
+      </c>
+      <c r="J2" s="13"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
@@ -10068,11 +10804,11 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
-      <c r="U2" s="17"/>
+      <c r="U2" s="15"/>
     </row>
     <row r="3" customFormat="1" spans="4:19">
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="4"/>
@@ -10107,7 +10843,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
-      <c r="J5" s="15"/>
+      <c r="J5" s="13"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -10169,7 +10905,7 @@
         <f t="shared" si="1"/>
         <v>132.86025</v>
       </c>
-      <c r="J7" s="16"/>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" customFormat="1" spans="1:10">
       <c r="A8" s="4">
@@ -10261,7 +10997,7 @@
       <c r="W12" s="6"/>
     </row>
     <row r="13" customFormat="1" spans="1:23">
-      <c r="A13" s="23">
+      <c r="A13" s="20">
         <v>6065.3041</v>
       </c>
       <c r="B13">
@@ -10296,7 +11032,7 @@
         <f>C13*1.1</f>
         <v>275</v>
       </c>
-      <c r="J14" s="16"/>
+      <c r="J14" s="14"/>
     </row>
     <row r="15" customFormat="1" spans="1:10">
       <c r="A15" s="4">
@@ -10477,7 +11213,7 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="23">
+      <c r="A30" s="20">
         <v>6065.3041</v>
       </c>
       <c r="B30">
@@ -10491,10 +11227,10 @@
         <f>C30</f>
         <v>4089.7624</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>0</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>0</v>
       </c>
     </row>
@@ -10511,11 +11247,11 @@
         <f>C30*1.1</f>
         <v>4498.73864</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <f>(A31-A30)/A30*C30</f>
         <v>-204.48812</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <f>E31/SUM(C30:C31)</f>
         <v>-0.0238095238095239</v>
       </c>
@@ -10533,11 +11269,11 @@
         <f>C30*1.2</f>
         <v>4907.71488</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <f>(A32-A30)/A30*C30+(A32-A31)/A31*A31</f>
         <v>-712.241445</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <f>E32/SUM(C30:C32)</f>
         <v>-0.0527734180619126</v>
       </c>
@@ -10555,11 +11291,11 @@
         <f>C30*1.3</f>
         <v>5316.69112</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <f>(A33-A30)/A30*C30+(A33-A31)/A31*C31+(A33-A32)/A32*C32</f>
         <v>-1359.66662245614</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <f>E33/SUM(C30:C33)</f>
         <v>-0.0722730739893211</v>
       </c>
@@ -10577,11 +11313,11 @@
         <f>C30*1.4</f>
         <v>5725.66736</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <f>(A34-A30)/A30*C30+(A34-A31)/A31*C31+(A34-A32)/A32*C32+(A34-A33)/A33*C33</f>
         <v>-2386.32782348813</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <f>E34/SUM(C30:C34)</f>
         <v>-0.0972480220158238</v>
       </c>
@@ -10599,11 +11335,11 @@
         <f>C30*1.5</f>
         <v>6134.6436</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="11">
         <f>(A35-A30)/A30*C30+(A35-A31)/A31*C31+(A35-A32)/A32*C32+(A35-A33)/A33*C33+(A35-A34)/A34*C34</f>
         <v>-3770.84323452012</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <f>E35/SUM(C30:C35)</f>
         <v>-0.122936016511868</v>
       </c>
@@ -10613,7 +11349,7 @@
         <f>A30*0.7</f>
         <v>4245.71287</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="16">
         <f>(A36-A30)/A30</f>
         <v>-0.3</v>
       </c>
@@ -10621,11 +11357,11 @@
         <f>C30*1.6</f>
         <v>6543.61984</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="11">
         <f>(A36-A30)/A30*C30+(A36-A31)/A31*C31+(A36-A32)/A32*C32+(A36-A33)/A33*C33+(A36-A34)/A34*C34+(A36-A35)/A35*C35</f>
         <v>-5564.33488555211</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <f>E36/SUM(C30:C36)</f>
         <v>-0.149511221492646</v>
       </c>
@@ -10635,7 +11371,7 @@
         <f>A30*0.65</f>
         <v>3942.447665</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="16">
         <f>(A37-A30)/A30</f>
         <v>-0.35</v>
       </c>
@@ -10643,11 +11379,11 @@
         <f>C30*1.7</f>
         <v>6952.59608</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <f>(A37-A30)/A30*C30+(A37-A31)/A31*C31+(A37-A32)/A32*C32+(A37-A33)/A33*C33+(A37-A34)/A34*C34+(A37-A35)/A35*C35+(A37-A36)/A36*C36</f>
         <v>-7825.22795372697</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <f>E37/SUM(C30:C37)</f>
         <v>-0.177163872371561</v>
       </c>
@@ -10657,7 +11393,7 @@
         <f>A30*0.6</f>
         <v>3639.18246</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="16">
         <f>(A38-A30)/A30</f>
         <v>-0.4</v>
       </c>
@@ -10665,11 +11401,11 @@
         <f>C30*1.8</f>
         <v>7361.57232</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <f>(A38-A30)/A30*C30+(A38-A31)/A31*C31+(A38-A32)/A32*C32+(A38-A33)/A33*C33+(A38-A34)/A34*C34+(A38-A35)/A35*C35+(A38-A36)/A36*C36+(A38-A37)/A37*C37</f>
         <v>-10620.9361049787</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <f>E38/SUM(C30:C38)</f>
         <v>-0.206107679239037</v>
       </c>
@@ -10679,7 +11415,7 @@
         <f>A30*0.55</f>
         <v>3335.917255</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="16">
         <f>(A39-A30)/A30</f>
         <v>-0.45</v>
       </c>
@@ -10687,23 +11423,27 @@
         <f>C30*1.9</f>
         <v>7770.54856</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="11">
         <f>(A39-A30)/A30*C30+(A39-A31)/A31*C31+(A39-A32)/A32*C32+(A39-A33)/A33*C33+(A39-A34)/A34*C34+(A39-A35)/A35*C35+(A39-A36)/A36*C36+(A39-A37)/A37*C37+(A39-A38)/A38*C38</f>
         <v>-14030.1086162305</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <f>E39/SUM(C30:C39)</f>
         <v>-0.236589220359371</v>
       </c>
     </row>
     <row r="40" spans="5:6">
-      <c r="E40" s="21"/>
-      <c r="F40" s="24"/>
-    </row>
-    <row r="41" spans="3:3">
-      <c r="C41" s="12">
+      <c r="E40" s="19"/>
+      <c r="F40" s="21"/>
+    </row>
+    <row r="41" spans="3:4">
+      <c r="C41" s="10">
         <f>SUM(C30:C39)</f>
         <v>59301.5548</v>
+      </c>
+      <c r="D41" s="9">
+        <f>SUM(D30:D39)</f>
+        <v>4089.7624</v>
       </c>
     </row>
   </sheetData>
